--- a/data.mn/public/datasets/mrpam-petroleum-imports.xlsx
+++ b/data.mn/public/datasets/mrpam-petroleum-imports.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L68"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2815,6 +2815,78 @@
         <v>203292</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>15321</v>
+      </c>
+      <c r="C69" t="n">
+        <v>154252</v>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="n">
+        <v>65207</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2730</v>
+      </c>
+      <c r="G69" t="n">
+        <v>980</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="n">
+        <v>4186</v>
+      </c>
+      <c r="J69" t="n">
+        <v>3367</v>
+      </c>
+      <c r="K69" t="n">
+        <v>27161</v>
+      </c>
+      <c r="L69" t="n">
+        <v>273205</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>19590</v>
+      </c>
+      <c r="C70" t="n">
+        <v>183205</v>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="n">
+        <v>54678</v>
+      </c>
+      <c r="F70" t="n">
+        <v>9896</v>
+      </c>
+      <c r="G70" t="n">
+        <v>5</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="n">
+        <v>9425</v>
+      </c>
+      <c r="J70" t="n">
+        <v>3822</v>
+      </c>
+      <c r="K70" t="n">
+        <v>32260</v>
+      </c>
+      <c r="L70" t="n">
+        <v>312881</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2826,7 +2898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L68"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5227,6 +5299,78 @@
         <v>2367</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>2730</v>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="n">
+        <v>65207</v>
+      </c>
+      <c r="E69" t="n">
+        <v>980</v>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="n">
+        <v>27161</v>
+      </c>
+      <c r="H69" t="n">
+        <v>154252</v>
+      </c>
+      <c r="I69" t="n">
+        <v>15321</v>
+      </c>
+      <c r="J69" t="n">
+        <v>273205</v>
+      </c>
+      <c r="K69" t="n">
+        <v>4186</v>
+      </c>
+      <c r="L69" t="n">
+        <v>3367</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>9896</v>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="n">
+        <v>54678</v>
+      </c>
+      <c r="E70" t="n">
+        <v>5</v>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="n">
+        <v>32260</v>
+      </c>
+      <c r="H70" t="n">
+        <v>183205</v>
+      </c>
+      <c r="I70" t="n">
+        <v>19590</v>
+      </c>
+      <c r="J70" t="n">
+        <v>312881</v>
+      </c>
+      <c r="K70" t="n">
+        <v>9425</v>
+      </c>
+      <c r="L70" t="n">
+        <v>3822</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
